--- a/portal/repositorio/SAVORY/ZONAS_SAVORY.xlsx
+++ b/portal/repositorio/SAVORY/ZONAS_SAVORY.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yembe\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yembe\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4BC45C4C-8B8D-4597-A6ED-23FAD5660961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E444DC90-A516-4F0F-8910-A4AB95B92517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{41A2F5D2-2D4B-4481-ABD1-94C660D6BEF3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="365">
   <si>
     <t>ZONA</t>
   </si>
@@ -1116,6 +1116,21 @@
   </si>
   <si>
     <t>PELEQUEN</t>
+  </si>
+  <si>
+    <t>PEÑAFLOR</t>
+  </si>
+  <si>
+    <t>VICUÑA</t>
+  </si>
+  <si>
+    <t>COMBARBALA</t>
+  </si>
+  <si>
+    <t>MONTE PATRIA</t>
+  </si>
+  <si>
+    <t>DOÑIHUE</t>
   </si>
 </sst>
 </file>
@@ -1192,43 +1207,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1569,9 +1554,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6A28D69-2729-49CB-BB03-3096C56CC23F}">
-  <dimension ref="A1:B337"/>
+  <dimension ref="A1:D342"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="33.109375" customWidth="1"/>
     <col min="2" max="2" width="11.5546875" style="5"/>
   </cols>
   <sheetData>
@@ -4263,12 +4249,53 @@
         <v>358</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
         <v>236</v>
       </c>
       <c r="B337" s="5" t="s">
         <v>359</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A338" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B338" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="D338" s="5"/>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A339" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B339" s="5" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A340" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B340" s="5" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A341" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B341" s="5" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A342" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B342" s="5" t="s">
+        <v>364</v>
       </c>
     </row>
   </sheetData>
